--- a/past_data/site_8024/2026-09-01.xlsx
+++ b/past_data/site_8024/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
+    <t>146.3</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
     <t>81.8</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>0.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>210.8</t>
+  </si>
+  <si>
+    <t>292.6</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -445,16 +463,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -462,19 +480,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -482,19 +500,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -502,19 +520,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -522,19 +540,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -542,19 +560,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -562,19 +580,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -582,19 +600,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -602,19 +620,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -622,19 +640,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -642,19 +660,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -662,19 +680,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -682,19 +700,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -702,19 +720,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -722,19 +740,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -742,19 +760,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -762,19 +780,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -782,19 +800,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -802,19 +820,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -822,19 +840,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -842,19 +860,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -862,19 +880,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -882,19 +900,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -902,19 +920,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -922,19 +940,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -942,19 +960,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -962,19 +980,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -982,19 +1000,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1002,19 +1020,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1022,19 +1040,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-09-01.xlsx
+++ b/past_data/site_8024/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="51">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>146.3</t>
+    <t>276.2</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>1.5</t>
+    <t>2.8</t>
   </si>
   <si>
     <t>01일</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>536.0</t>
+  </si>
+  <si>
+    <t>828.6</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -506,13 +518,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -520,19 +532,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -540,19 +552,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -560,19 +572,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -580,19 +592,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -600,19 +612,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -620,19 +632,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -640,19 +652,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -660,19 +672,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -680,19 +692,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -700,19 +712,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -720,19 +732,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -740,19 +752,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -760,19 +772,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -780,19 +792,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -800,19 +812,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -820,19 +832,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -840,19 +852,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -860,19 +872,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -880,19 +892,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -900,19 +912,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -920,19 +932,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -940,19 +952,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -960,19 +972,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -980,19 +992,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1000,19 +1012,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1020,19 +1032,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1040,19 +1052,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-09-01.xlsx
+++ b/past_data/site_8024/2026-09-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="55">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>276.2</t>
+    <t>344.1</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2.8</t>
+    <t>3.4</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>547.8</t>
+  </si>
+  <si>
+    <t>1376.4</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>13.8</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -538,13 +550,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -552,19 +564,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -572,19 +584,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -592,19 +604,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -612,19 +624,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -632,19 +644,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -652,19 +664,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -672,19 +684,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -692,19 +704,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -712,19 +724,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -732,19 +744,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -752,19 +764,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -772,19 +784,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -792,19 +804,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -812,19 +824,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -832,19 +844,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -852,19 +864,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -872,19 +884,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -892,19 +904,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -912,19 +924,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -932,19 +944,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -952,19 +964,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -972,19 +984,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -992,19 +1004,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1012,19 +1024,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1032,19 +1044,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1052,19 +1064,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
